--- a/series_data/could-you-survive/series_log.xlsx
+++ b/series_data/could-you-survive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -837,6 +837,356 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-07-14 19:55</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/c5f425fa44ceed4c71fc9dcfe33f5d1e.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-07-14 19:57</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/a8ee92838465cb3d8527f28eb8a4f51f.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-07-14 20:00</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6ef28f3577221e09949b26fe0dd0d5e3_1784059179.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-07-14 20:05</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5388dbc714b56519d1da2b8c5013d5f7_1784059345.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-07-14 20:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/73733695d88cb78f6d97715aa27a5c71_1784059833.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep02/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-07-14 20:14</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/vw/3ff8ea7faf769ed0c50697c86a16f72b.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep02/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/could-you-survive/series_log.xlsx
+++ b/series_data/could-you-survive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1187,6 +1187,352 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-07-15 19:48</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/49a5709b9de3e14527c7b0660df7c176_1784144850.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-07-15 19:50</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/509964c8cede0a80e01951a5702b6d83_1784144988.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-07-15 19:53</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/62983398ee5d3962f6d5831f9d863c34_1784145144.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-07-15 19:59</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b942cded6f5f1a155968d865fdb2ce2d_1784145300.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-07-15 20:05</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/11cac30ee9f6c3bd014ba63826f5bbc3_1784145757.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep03/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-07-15 20:07</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/12b5765e51a637019a768d5a7599e096_1784146032.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep03/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/could-you-survive/series_log.xlsx
+++ b/series_data/could-you-survive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1533,6 +1533,344 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:48</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>315.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>1.575</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/819b90d5949621b34e7b449e1cec776a_1784230978.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:52</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3f77031c2143bd04e7acf8ab08574cef_1784231407.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:55</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1b6a6ed8f40b259e6d89c6c7d9c48463_1784231686.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:57</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0d253471626f9c58ea3f3c3be572310f_1784231817.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-07-16 20:06</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep04/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-07-16 20:11</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>qc_fail</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/61580abac6cf3c6264cb1c298f0ed3a9_1784232651.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep04/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/series_data/could-you-survive/series_log.xlsx
+++ b/series_data/could-you-survive/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1871,6 +1871,356 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-07-17 19:50</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/bbe8d65e3c199d696ec6bd960ffe9819_1784317583.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-07-17 19:59</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cf3c5e9e77c50fa0609a3db47cc201d4_1784318314.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-07-17 20:01</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/058d30e1d3e06e8ee509858bfd9926c9_1784318475.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-07-17 20:04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/599407ed6b9d16a879967b187511bac2_1784318615.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-07-17 20:07</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.525</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/fd80b436f0975c946668ceb634a28568_1784318823.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep05/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-07-17 20:12</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Ihsan</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>210.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/44605e8968ee6a76f8cdd3394d1c6a3e_1784318977.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/could-you-survive/episodes/ep05/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
